--- a/光伏配储项目/电价数据/2026/牛山站.xlsx
+++ b/光伏配储项目/电价数据/2026/牛山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50993</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.53284</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5438</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43862</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45544</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44023</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42368</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40928</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41371</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39265</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41506</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41352</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29469</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>-0.01294</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.11439</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.031</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.02309</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03648</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08258</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00567</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14441</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21161</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23905</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.15083</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.01376</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1188</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.01254</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.09344</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.25295</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.07876000000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.18508</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42815</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.17955</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.07263</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.24208</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.56065</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6034700000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.22377</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.28535</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.29217</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47874</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42085</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.43959</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.1532</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.69251</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79439</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53661</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50637</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.46481</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50012</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.37379</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47385</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.35536</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37171</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5138200000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.62388</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7251799999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43611</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.13011</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.16567</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.12341</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.25721</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.19445</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.14797</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.12587</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.29691</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.16268</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00102</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.11591</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.14296</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.25528</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.21004</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>-0.00256</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.03154</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>-0.01354</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22713</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24851</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.25519</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6792</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.78152</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.76701</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7877000000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.47536</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.13483</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.6007100000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33312</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5164500000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48553</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.4343</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44456</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34682</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21094</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.29446</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.01391</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.26237</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24868</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28082</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.27385</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25798</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.13733</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.09175</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.23019</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27488</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.16903</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.20167</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.15611</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.00384</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.08527999999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.05565</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.26847</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.18454</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.26455</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>-0.00536</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.07743000000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.21302</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.05538000000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.14167</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.09089</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.10085</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.24109</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.22379</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.27646</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34321</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.09692000000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.24908</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.24904</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46911</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29937</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26502</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.05377000000000001</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.00534</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.03534</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.009630000000000001</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.23415</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>-0.04616</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.07353</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.1669</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.12413</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.00388</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.03872999999999999</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.02304</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.02883</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.09059</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>-0.02238</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.16027</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.27794</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.27833</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.03025</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.1692</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>-0.00776</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29585</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28702</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28957</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27821</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.02479</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.03643</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04415</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.03932</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.01927</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04462</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04837</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.0498</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14824</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>-0.00076</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28725</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.14702</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.18594</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.17655</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.21021</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.11581</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.27657</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.21773</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.30387</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39849</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40979</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4675299999999999</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41341</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34891</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.24842</v>
+      </c>
+      <c r="D122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E122" t="n">
+        <v>-0.01329</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.28606</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3096</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.28174</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29951</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0466</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04572</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04505</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04321</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04218</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04464</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10104</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00267</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04582</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04871</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04488</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04838</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04877</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04243</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04478</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04915</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.07088</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.17721</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.23638</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.25424</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.25469</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.24694</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.1441</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2161</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.19259</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.21157</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.22183</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.19552</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.21681</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.1963</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.25836</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33051</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31866</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.25842</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.10218</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29155</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.24676</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.24567</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.08069</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.05913</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17177</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14839</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16012</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15935</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23739</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21477</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.17537</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.11956</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.27626</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.25831</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.25494</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>-0.04272</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.25638</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.0144</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.11943</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.07257</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>-0.00318</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.14982</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>-0.00214</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.05283</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.10779</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.17746</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.2741</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>-0.04618</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.16654</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.07751000000000001</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.20475</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.73964</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.48972</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.23504</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.57543</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.52035</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.20753</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.48885</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>0.9346100000000001</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>-0.01294</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.48934</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>0.68952</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.47442</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>0.9810800000000001</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>0.6999299999999999</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79003</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77676</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87854</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8733500000000001</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49223</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39912</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20624</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87936</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5513400000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63895</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49862</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45901</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42747</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45402</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42115</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43394</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39185</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5870599999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42765</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59622</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.45366</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6550499999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.82343</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>-0.04242</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>-0.0485</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.83084</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>-0.04692</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>-0.04672</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>-0.04805</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>-0.04968</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>-0.04671</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.09934</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.10082</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.07196999999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.09320999999999999</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.06434999999999999</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.0824</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.04414</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.06369</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.13949</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.07226</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.05072</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.0653</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>-0.02504</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.06781999999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.07731</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.12854</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.13447</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.11798</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.22391</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.28841</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45348</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35434</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9549500000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.47726</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50004</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.06191</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.22813</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>-0.04785</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.25991</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.04583</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.09691</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.27125</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.25148</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.1019</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25421</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28259</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4017</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5967</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88527</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33319</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13549</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70345</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6496799999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58348</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43745</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42349</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4341</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.01118</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.23396</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.17436</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>-0.04618999999999999</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.2217</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.23159</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.19144</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.0396</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>-0.00642</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>-0.00775</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>-0.02898</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>-0.0425</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.13227</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.05596</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.03191</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.19625</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32475</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32618</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32943</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39994</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.27299</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.04046</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14926</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14802</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15271</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.57262</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.60563</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14435</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14434</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14174</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14868</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27787</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14683</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.13167</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11779</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11832</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.17496</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14552</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15362</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40643</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45045</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44079</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43987</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44416</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34931</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.54244</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46864</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38017</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28523</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.04137</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.03476</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23552</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24401</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26258</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.28492</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.2545</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22802</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.2879</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.27332</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.31952</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.28722</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31153</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.29627</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.18331</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3543</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41958</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38035</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36024</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31353</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.27565</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.26117</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.25401</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.32094</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2383</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24909</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.18541</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.06977999999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.16812</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24117</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.25395</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.23678</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.28454</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.25593</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.2805299999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.30446</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.39594</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47096</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.38735</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70785</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.26378</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31444</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29749</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29086</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30721</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36794</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39368</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40324</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34923</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35595</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.57625</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36235</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37636</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6513300000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83356</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47292</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34483</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41158</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.3709</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37955</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35823</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26011</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13199</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19456</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24385</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2784</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.04838</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.12612</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.22546</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.23673</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14256</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.19486</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.20497</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27615</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3102200000000001</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29205</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.63613</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6025900000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5925199999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45534</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.62175</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.45387</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42904</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47741</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41971</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37914</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36017</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48994</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.42021</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.42619</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4186</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40092</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41298</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41069</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41721</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56087</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50078</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.40974</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.19593</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.3512</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43859</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.18821</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.01041</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.01309</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.20614</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.08781</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.04232</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.25157</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.26414</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.71057</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.23304</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.09178</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.03986</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.20879</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48044</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42296</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50517</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50646</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.5180399999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.60637</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.52585</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71109</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.45945</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5319400000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.80703</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7425499999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.59372</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64219</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48007</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47948</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47283</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49951</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.4584</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45771</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39367</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36829</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.2245</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.24067</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15508</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.19733</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.06211</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.23888</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41903</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.47358</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47621</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.01295</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18996</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34829</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40876</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39684</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40583</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40106</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36407</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44232</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31943</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37675</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.13044</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23142</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23297</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24606</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>-0.02447</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.12944</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.22438</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.02381</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.14895</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04338</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25508</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.03652</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14223</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15123</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.004849999999999999</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30315</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21559</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22634</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.13875</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21043</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26483</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25786</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36607</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35195</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22769</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21718</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15126</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.1807</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01458</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00314</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04202</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03399</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04309</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04996</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.17019</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21506</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26743</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24257</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24503</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.2448</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.2871</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27259</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26908</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2582</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30358</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.27748</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.2813</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27423</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.36343</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30167</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25248</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.23699</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.19113</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05752</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.03491</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06692000000000001</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.25062</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22751</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22491</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.1489</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.26359</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24609</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22333</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20691</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.19034</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21517</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.17052</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.19045</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22288</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.22268</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24406</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23234</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21553</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26385</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22714</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.27145</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24713</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18448</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06659000000000001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.4977200000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.50183</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.50589</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.18413</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.19667</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.09853000000000001</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.04408</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.04893</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.00584</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20768</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29131</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02734</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.13169</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03954</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.04292</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.00142</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07482999999999999</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02675</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.02129</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02285</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.05264</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.19227</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.25444</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.20733</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.25809</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.26281</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.28837</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30294</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.26392</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.25827</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.29388</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36185</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32926</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32496</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.08729000000000001</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34163</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>-0.01068</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>-0.01961</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>-0.01086</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>-0.02575</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.23848</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.26562</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.27586</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.28116</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.28712</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.10016</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.21467</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26943</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.14951</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.13849</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.04784</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>-0.0193</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33078</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2634</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36961</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>-0.00958</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.42969</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.52324</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.26541</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.2108</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.23721</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.2248</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.20543</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.20695</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.20644</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.23872</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.24346</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.17397</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.2295</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.25715</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.22716</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.24929</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.43214</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.41169</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.43214</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.27673</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.70508</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45864</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38007</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36876</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44339</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38077</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3756</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.08990999999999999</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>-0.02833</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.02076</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.03511</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>-0.02018</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.09154000000000001</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.16885</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29332</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.25981</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.14947</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.15211</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.18525</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.01849</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.07210999999999999</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.26382</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.28726</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.43019</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52863</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.52375</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.45861</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54886</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.42824</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.44347</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.49725</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.47856</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70913</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74829</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5171</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5189900000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37524</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27138</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30997</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29276</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.29169</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27508</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25968</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27558</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20644</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23228</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13553</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01292</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02405</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.24187</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02018</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03468</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02542</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00993</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>-0.00075</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.12132</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11237</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.20668</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18543</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.10847</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.23708</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.23046</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.22108</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37406</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.39992</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.26803</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37615</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.76415</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40331</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35601</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.23781</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.21604</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.20708</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.17548</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.17522</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.18056</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.23404</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.06444</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01757</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.02852</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.02733</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.01415</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.08278000000000001</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.01219</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.02849</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01443</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.03205</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.03969</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.02304</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.03918</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>-0.03857</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.02645</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13411</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>-0.01377</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.14311</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.16309</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>-0.01357</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.01273</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.01379</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.07790000000000001</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.46246</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.47915</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.43742</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5350199999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.46913</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44339</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.39066</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.49921</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25865</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.22325</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.20371</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.13546</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.18223</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.20954</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13143</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.14078</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.0181</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.11372</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03275</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03484</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.03615</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.03904</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.03135</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.01334</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03691</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>-0.02481</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.03363</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.04329</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.08708</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>-0.04651</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.042</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.03309</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.04098</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.03297</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.02407</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.03754</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>-0.03709</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>-0.03676</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>-0.02681</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.18321</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23649</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.24026</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.24647</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.26181</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30198</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47939</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41944</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38401</v>
       </c>
     </row>
   </sheetData>
